--- a/zym/示例数据/批次库存表模板.xlsx
+++ b/zym/示例数据/批次库存表模板.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库存销售表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'库存销售表'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'库存销售表'!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,20 +437,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,55 +468,65 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>当前库存</t>
+          <t>上次进货总量</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>本进货周期销量</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>库存剩余量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>近7天销量</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>近30天销量</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>保质期（天）</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>标注到期日期</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>货架位置</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>仓库位置</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>条码</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>品类</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="J2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>